--- a/site/leagues/betclic/2026_2027/xlsx/shot_packs/shot_pack_CAQ.xlsx
+++ b/site/leagues/betclic/2026_2027/xlsx/shot_packs/shot_pack_CAQ.xlsx
@@ -654,7 +654,7 @@
         </is>
       </c>
       <c r="S2" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="T2" t="n">
         <v>3</v>
@@ -663,10 +663,10 @@
         <v>3</v>
       </c>
       <c r="V2" t="n">
+        <v>11</v>
+      </c>
+      <c r="W2" t="n">
         <v>4</v>
-      </c>
-      <c r="W2" t="n">
-        <v>3</v>
       </c>
     </row>
   </sheetData>

--- a/site/leagues/betclic/2026_2027/xlsx/shot_packs/shot_pack_CAQ.xlsx
+++ b/site/leagues/betclic/2026_2027/xlsx/shot_packs/shot_pack_CAQ.xlsx
@@ -22,12 +22,12 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'overview'!$A$1:$W$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'alerts'!$A$1:$B$6</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'players_volume'!$A$1:$S$10</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'players_eff'!$A$1:$S$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'players_eff'!$A$1:$S$7</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'players_3pt_volume'!$A$1:$N$10</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'players_3pt_pct'!$A$1:$N$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'team_zones'!$A$1:$I$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'team_zones'!$A$1:$I$7</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'preferred_areas'!$A$1:$P$10</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'player_zones_volume'!$A$1:$K$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'player_zones_volume'!$A$1:$K$13</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'player_zones_pct'!$A$1:$K$2</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -448,10 +448,10 @@
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
     <col width="14" customWidth="1" min="12" max="12"/>
-    <col width="17" customWidth="1" min="13" max="13"/>
+    <col width="19" customWidth="1" min="13" max="13"/>
     <col width="16" customWidth="1" min="14" max="14"/>
     <col width="16" customWidth="1" min="15" max="15"/>
-    <col width="19" customWidth="1" min="16" max="16"/>
+    <col width="14" customWidth="1" min="16" max="16"/>
     <col width="16" customWidth="1" min="17" max="17"/>
     <col width="16" customWidth="1" min="18" max="18"/>
     <col width="25" customWidth="1" min="19" max="19"/>
@@ -590,38 +590,38 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>72</v>
+        <v>132</v>
       </c>
       <c r="D2" t="n">
-        <v>35</v>
+        <v>62</v>
       </c>
       <c r="E2" t="n">
+        <v>142</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>47.0%</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
         <v>82</v>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>48.6%</t>
-        </is>
-      </c>
-      <c r="G2" t="n">
-        <v>41</v>
-      </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>56.1%</t>
+          <t>53.7%</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>31</v>
+        <v>50</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>38.7%</t>
+          <t>36.0%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>43.1%</t>
+          <t>37.9%</t>
         </is>
       </c>
       <c r="L2" t="n">
@@ -629,32 +629,32 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="N2" t="n">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>59.3%</t>
+          <t>32.5%</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Paint Non-RA</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>38.5%</t>
+          <t>52.6%</t>
         </is>
       </c>
       <c r="S2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="T2" t="n">
         <v>3</v>
@@ -663,10 +663,10 @@
         <v>3</v>
       </c>
       <c r="V2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="W2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -771,25 +771,25 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F2" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>44.4%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>46.2%</t>
         </is>
       </c>
       <c r="J2" t="n">
@@ -838,7 +838,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Maior volume: A. Thiam (15 L)</t>
+          <t>Maior volume: A. Thiam (26 L)</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Maior volume 3pt: A. Thiam (12 3PA)</t>
+          <t>Maior volume 3pt: A. Thiam (18 3PA)</t>
         </is>
       </c>
     </row>
@@ -862,7 +862,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Mais eficaz: J. Shoats (2 pts/shot)</t>
+          <t>Mais eficaz: J. Shoats (1.7 pts/shot)</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Zona mais usada: Restricted Area (27 L)</t>
+          <t>Zona mais usada: Above the Break 3 (40 L)</t>
         </is>
       </c>
     </row>
@@ -886,7 +886,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Zona mais eficaz: Restricted Area (59.3%)</t>
+          <t>Zona mais eficaz: Restricted Area (62.5%)</t>
         </is>
       </c>
     </row>
@@ -1035,46 +1035,46 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="D2" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E2" t="n">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>42.3%</t>
         </is>
       </c>
       <c r="G2" t="n">
+        <v>18</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>69.2%</t>
+        </is>
+      </c>
+      <c r="J2" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="L2" t="n">
         <v>12</v>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>41.7%</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>80.0%</t>
-        </is>
-      </c>
-      <c r="J2" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
-      <c r="L2" t="n">
-        <v>9</v>
-      </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>44.4%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -1083,18 +1083,18 @@
         </is>
       </c>
       <c r="O2" t="n">
+        <v>4</v>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>25.0%</t>
+        </is>
+      </c>
+      <c r="Q2" t="n">
+        <v>1</v>
+      </c>
+      <c r="R2" t="n">
         <v>3</v>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>33.3%</t>
-        </is>
-      </c>
-      <c r="Q2" t="n">
-        <v>1</v>
-      </c>
-      <c r="R2" t="n">
-        <v>2</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -1112,34 +1112,34 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="D3" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E3" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>46.2%</t>
+          <t>36.4%</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>23.1%</t>
+          <t>40.9%</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -1156,50 +1156,50 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>Mid-Range</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="O3" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="Q3" t="n">
         <v>2</v>
       </c>
       <c r="R3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="S3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>CAQ_D._BACCHUS</t>
+          <t>CAQ_J._SHOATS</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>D. Bacchus</t>
+          <t>J. Shoats</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="D4" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="E4" t="n">
-        <v>12</v>
+        <v>36</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>41.7%</t>
+          <t>81.0%</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1212,11 +1212,11 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>19.0%</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>1</v>
+        <v>1.7</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -1224,49 +1224,49 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Paint Non-RA</t>
         </is>
       </c>
       <c r="O4" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>85.7%</t>
         </is>
       </c>
       <c r="Q4" t="n">
         <v>3</v>
       </c>
       <c r="R4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="S4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>CAQ_J._SHOATS</t>
+          <t>CAQ_D._BACCHUS</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>J. Shoats</t>
+          <t>D. Bacchus</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="D5" t="n">
         <v>10</v>
@@ -1276,56 +1276,56 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>90.9%</t>
+          <t>47.6%</t>
         </is>
       </c>
       <c r="G5" t="n">
+        <v>6</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>28.6%</t>
+        </is>
+      </c>
+      <c r="J5" t="n">
+        <v>1</v>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="L5" t="n">
+        <v>7</v>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>85.7%</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="O5" t="n">
+        <v>7</v>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>28.6%</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
         <v>3</v>
       </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>66.7%</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>27.3%</t>
-        </is>
-      </c>
-      <c r="J5" t="n">
-        <v>2</v>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>Restricted Area</t>
-        </is>
-      </c>
-      <c r="L5" t="n">
-        <v>6</v>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
-      <c r="O5" t="n">
-        <v>3</v>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>66.7%</t>
-        </is>
-      </c>
-      <c r="Q5" t="n">
+      <c r="R5" t="n">
         <v>4</v>
-      </c>
-      <c r="R5" t="n">
-        <v>1</v>
       </c>
       <c r="S5" t="n">
         <v>4</v>
@@ -1334,124 +1334,124 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>CAQ_D._RIDGNAL</t>
+          <t>CAQ_D._HORTA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>D. Ridgnal</t>
+          <t>D. Horta</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="D6" t="n">
+        <v>3</v>
+      </c>
+      <c r="E6" t="n">
+        <v>8</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>23.1%</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>7</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>28.6%</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>53.8%</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="L6" t="n">
+        <v>7</v>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>28.6%</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="O6" t="n">
         <v>4</v>
       </c>
-      <c r="E6" t="n">
-        <v>9</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>66.7%</t>
-        </is>
-      </c>
-      <c r="G6" t="n">
-        <v>2</v>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>50.0%</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>33.3%</t>
-        </is>
-      </c>
-      <c r="J6" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>Restricted Area</t>
-        </is>
-      </c>
-      <c r="L6" t="n">
-        <v>2</v>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>Paint Non-RA</t>
-        </is>
-      </c>
-      <c r="O6" t="n">
-        <v>2</v>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="Q6" t="n">
         <v>5</v>
       </c>
       <c r="R6" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="S6" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>CAQ_D._HORTA</t>
+          <t>CAQ_I._PAVICEVIC</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>D. Horta</t>
+          <t>I. Pavicevic</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="D7" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E7" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>63.6%</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>83.3%</t>
+          <t>9.1%</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>0.5</v>
+        <v>1.4</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Paint Non-RA</t>
         </is>
       </c>
       <c r="L7" t="n">
@@ -1459,72 +1459,72 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>60.0%</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="O7" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>60.0%</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="R7" t="n">
+        <v>2</v>
+      </c>
+      <c r="S7" t="n">
         <v>7</v>
-      </c>
-      <c r="S7" t="n">
-        <v>2</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>CAQ_I._PAVICEVIC</t>
+          <t>CAQ_D._RIDGNAL</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>I. Pavicevic</t>
+          <t>D. Ridgnal</t>
         </is>
       </c>
       <c r="C8" t="n">
+        <v>9</v>
+      </c>
+      <c r="D8" t="n">
         <v>5</v>
       </c>
-      <c r="D8" t="n">
+      <c r="E8" t="n">
+        <v>11</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>55.6%</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
         <v>3</v>
       </c>
-      <c r="E8" t="n">
-        <v>7</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>60.0%</t>
-        </is>
-      </c>
-      <c r="G8" t="n">
-        <v>1</v>
-      </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -1536,20 +1536,20 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Paint Non-RA</t>
         </is>
       </c>
       <c r="O8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="Q8" t="n">
@@ -1559,7 +1559,7 @@
         <v>3</v>
       </c>
       <c r="S8" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9">
@@ -1574,7 +1574,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
@@ -1597,7 +1597,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="J9" t="n">
@@ -1605,20 +1605,20 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="L9" t="n">
+        <v>3</v>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
           <t>Above the Break 3</t>
-        </is>
-      </c>
-      <c r="L9" t="n">
-        <v>1</v>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>Paint Non-RA</t>
         </is>
       </c>
       <c r="O9" t="n">
@@ -1633,7 +1633,7 @@
         <v>8</v>
       </c>
       <c r="R9" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="S9" t="n">
         <v>7</v>
@@ -1651,55 +1651,69 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>1</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
           <t>0.0%</t>
         </is>
       </c>
-      <c r="G10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr">
         <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Mid-Range</t>
+        </is>
+      </c>
+      <c r="L10" t="n">
+        <v>1</v>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="O10" t="n">
+        <v>1</v>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
           <t>0.0%</t>
         </is>
       </c>
-      <c r="J10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>Paint Non-RA</t>
-        </is>
-      </c>
-      <c r="L10" t="n">
-        <v>1</v>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
-      <c r="O10" t="inlineStr"/>
-      <c r="P10" t="inlineStr"/>
       <c r="Q10" t="n">
         <v>9</v>
       </c>
       <c r="R10" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="S10" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -1714,11 +1728,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S5"/>
+  <dimension ref="A1:S7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
@@ -1847,205 +1861,205 @@
         </is>
       </c>
       <c r="C2" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>81.0%</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>21</v>
+      </c>
+      <c r="F2" t="n">
+        <v>17</v>
+      </c>
+      <c r="G2" t="n">
+        <v>36</v>
+      </c>
+      <c r="H2" t="n">
+        <v>4</v>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>19.0%</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="L2" t="n">
+        <v>7</v>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="O2" t="n">
+        <v>7</v>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>85.7%</t>
+        </is>
+      </c>
+      <c r="Q2" t="n">
+        <v>1</v>
+      </c>
+      <c r="R2" t="n">
+        <v>3</v>
+      </c>
+      <c r="S2" t="n">
         <v>2</v>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>90.9%</t>
-        </is>
-      </c>
-      <c r="E2" t="n">
-        <v>11</v>
-      </c>
-      <c r="F2" t="n">
-        <v>10</v>
-      </c>
-      <c r="G2" t="n">
-        <v>22</v>
-      </c>
-      <c r="H2" t="n">
-        <v>3</v>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>66.7%</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>27.3%</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>Restricted Area</t>
-        </is>
-      </c>
-      <c r="L2" t="n">
-        <v>6</v>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
-      <c r="O2" t="n">
-        <v>3</v>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>66.7%</t>
-        </is>
-      </c>
-      <c r="Q2" t="n">
-        <v>1</v>
-      </c>
-      <c r="R2" t="n">
-        <v>4</v>
-      </c>
-      <c r="S2" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>CAQ_A._THIAM</t>
+          <t>CAQ_I._PAVICEVIC</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>A. Thiam</t>
+          <t>I. Pavicevic</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1.1</v>
+        <v>1.4</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>63.6%</t>
         </is>
       </c>
       <c r="E3" t="n">
+        <v>11</v>
+      </c>
+      <c r="F3" t="n">
+        <v>7</v>
+      </c>
+      <c r="G3" t="n">
         <v>15</v>
       </c>
-      <c r="F3" t="n">
-        <v>6</v>
-      </c>
-      <c r="G3" t="n">
-        <v>17</v>
-      </c>
       <c r="H3" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>41.7%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>9.1%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Paint Non-RA</t>
         </is>
       </c>
       <c r="L3" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>44.4%</t>
+          <t>60.0%</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>Corner 3 Left</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="O3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>60.0%</t>
         </is>
       </c>
       <c r="Q3" t="n">
         <v>2</v>
       </c>
       <c r="R3" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="S3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>CAQ_D._BACCHUS</t>
+          <t>CAQ_A._THIAM</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>D. Bacchus</t>
+          <t>A. Thiam</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>41.7%</t>
+          <t>42.3%</t>
         </is>
       </c>
       <c r="E4" t="n">
+        <v>26</v>
+      </c>
+      <c r="F4" t="n">
+        <v>11</v>
+      </c>
+      <c r="G4" t="n">
+        <v>31</v>
+      </c>
+      <c r="H4" t="n">
+        <v>18</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>69.2%</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="L4" t="n">
         <v>12</v>
       </c>
-      <c r="F4" t="n">
-        <v>5</v>
-      </c>
-      <c r="G4" t="n">
-        <v>12</v>
-      </c>
-      <c r="H4" t="n">
-        <v>4</v>
-      </c>
-      <c r="I4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>50.0%</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>33.3%</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>Restricted Area</t>
-        </is>
-      </c>
-      <c r="L4" t="n">
-        <v>6</v>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>33.3%</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Corner 3 Left</t>
         </is>
       </c>
       <c r="O4" t="n">
@@ -2053,14 +2067,14 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="Q4" t="n">
         <v>3</v>
       </c>
       <c r="R4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="S4" t="n">
         <v>2</v>
@@ -2069,82 +2083,236 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>CAQ_J._THOMAS</t>
+          <t>CAQ_D._BACCHUS</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>J. Thomas</t>
+          <t>D. Bacchus</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>46.2%</t>
+          <t>47.6%</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="F5" t="n">
+        <v>10</v>
+      </c>
+      <c r="G5" t="n">
+        <v>22</v>
+      </c>
+      <c r="H5" t="n">
         <v>6</v>
       </c>
-      <c r="G5" t="n">
-        <v>12</v>
-      </c>
-      <c r="H5" t="n">
-        <v>3</v>
-      </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>23.1%</t>
+          <t>28.6%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="L5" t="n">
+        <v>7</v>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>85.7%</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
           <t>Restricted Area</t>
         </is>
       </c>
-      <c r="L5" t="n">
-        <v>6</v>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>66.7%</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>Mid-Range</t>
-        </is>
-      </c>
       <c r="O5" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>28.6%</t>
         </is>
       </c>
       <c r="Q5" t="n">
         <v>4</v>
       </c>
       <c r="R5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S5" t="n">
         <v>4</v>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>CAQ_J._THOMAS</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>J. Thomas</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>36.4%</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>22</v>
+      </c>
+      <c r="F6" t="n">
+        <v>8</v>
+      </c>
+      <c r="G6" t="n">
+        <v>17</v>
+      </c>
+      <c r="H6" t="n">
+        <v>9</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>11.1%</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>40.9%</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="L6" t="n">
+        <v>6</v>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>66.7%</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="O6" t="n">
+        <v>6</v>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>5</v>
+      </c>
+      <c r="R6" t="n">
+        <v>2</v>
+      </c>
+      <c r="S6" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>CAQ_D._HORTA</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>D. Horta</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>23.1%</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>13</v>
+      </c>
+      <c r="F7" t="n">
+        <v>3</v>
+      </c>
+      <c r="G7" t="n">
+        <v>8</v>
+      </c>
+      <c r="H7" t="n">
+        <v>7</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>28.6%</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>53.8%</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="L7" t="n">
+        <v>7</v>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>28.6%</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="O7" t="n">
+        <v>4</v>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>25.0%</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>6</v>
+      </c>
+      <c r="R7" t="n">
+        <v>5</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:S5"/>
+  <autoFilter ref="A1:S7"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2258,97 +2426,97 @@
         </is>
       </c>
       <c r="C2" t="n">
+        <v>18</v>
+      </c>
+      <c r="D2" t="n">
+        <v>9</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>69.2%</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>26</v>
+      </c>
+      <c r="H2" t="n">
+        <v>31</v>
+      </c>
+      <c r="I2" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="K2" t="n">
         <v>12</v>
       </c>
-      <c r="D2" t="n">
-        <v>5</v>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>41.7%</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>80.0%</t>
-        </is>
-      </c>
-      <c r="G2" t="n">
-        <v>15</v>
-      </c>
-      <c r="H2" t="n">
-        <v>17</v>
-      </c>
-      <c r="I2" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
-      <c r="K2" t="n">
-        <v>9</v>
-      </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>44.4%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="M2" t="n">
         <v>1</v>
       </c>
       <c r="N2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>CAQ_D._HORTA</t>
+          <t>CAQ_J._THOMAS</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>D. Horta</t>
+          <t>J. Thomas</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D3" t="n">
         <v>1</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>83.3%</t>
+          <t>40.9%</t>
         </is>
       </c>
       <c r="G3" t="n">
+        <v>22</v>
+      </c>
+      <c r="H3" t="n">
+        <v>17</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="K3" t="n">
         <v>6</v>
       </c>
-      <c r="H3" t="n">
-        <v>3</v>
-      </c>
-      <c r="I3" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
-      <c r="K3" t="n">
-        <v>5</v>
-      </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="M3" t="n">
@@ -2361,150 +2529,150 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>CAQ_D._BACCHUS</t>
+          <t>CAQ_D._HORTA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>D. Bacchus</t>
+          <t>D. Horta</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D4" t="n">
         <v>2</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>28.6%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>53.8%</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H4" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="I4" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="K4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>28.6%</t>
         </is>
       </c>
       <c r="M4" t="n">
         <v>3</v>
       </c>
       <c r="N4" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>CAQ_J._SHOATS</t>
+          <t>CAQ_D._BACCHUS</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>J. Shoats</t>
+          <t>D. Bacchus</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D5" t="n">
         <v>2</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>27.3%</t>
+          <t>28.6%</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="H5" t="n">
         <v>22</v>
       </c>
       <c r="I5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Paint Non-RA</t>
         </is>
       </c>
       <c r="K5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>85.7%</t>
         </is>
       </c>
       <c r="M5" t="n">
         <v>4</v>
       </c>
       <c r="N5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>CAQ_J._THOMAS</t>
+          <t>CAQ_J._SHOATS</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>J. Thomas</t>
+          <t>J. Shoats</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>23.1%</t>
+          <t>19.0%</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="H6" t="n">
-        <v>12</v>
+        <v>36</v>
       </c>
       <c r="I6" t="n">
-        <v>0.9</v>
+        <v>1.7</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -2512,18 +2680,18 @@
         </is>
       </c>
       <c r="K6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="M6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
@@ -2538,14 +2706,14 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D7" t="n">
         <v>1</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -2554,13 +2722,13 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="H7" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="I7" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -2568,7 +2736,7 @@
         </is>
       </c>
       <c r="K7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
@@ -2579,7 +2747,7 @@
         <v>6</v>
       </c>
       <c r="N7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="8">
@@ -2606,29 +2774,29 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>9.1%</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="H8" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="I8" t="n">
         <v>1.4</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Paint Non-RA</t>
         </is>
       </c>
       <c r="K8" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>60.0%</t>
         </is>
       </c>
       <c r="M8" t="n">
@@ -2662,11 +2830,11 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -2676,11 +2844,11 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Paint Non-RA</t>
         </is>
       </c>
       <c r="K9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
@@ -2691,7 +2859,7 @@
         <v>7</v>
       </c>
       <c r="N9" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="10">
@@ -2706,29 +2874,33 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D10" t="n">
         <v>0</v>
       </c>
-      <c r="E10" t="inlineStr"/>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Mid-Range</t>
         </is>
       </c>
       <c r="K10" t="n">
@@ -2736,13 +2908,15 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="M10" t="n">
-        <v>9</v>
-      </c>
-      <c r="N10" t="inlineStr"/>
+        <v>7</v>
+      </c>
+      <c r="N10" t="n">
+        <v>8</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:N10"/>
@@ -2859,48 +3033,48 @@
         </is>
       </c>
       <c r="C2" t="n">
+        <v>18</v>
+      </c>
+      <c r="D2" t="n">
+        <v>9</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>69.2%</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>26</v>
+      </c>
+      <c r="H2" t="n">
+        <v>31</v>
+      </c>
+      <c r="I2" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="K2" t="n">
         <v>12</v>
       </c>
-      <c r="D2" t="n">
-        <v>5</v>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>41.7%</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>80.0%</t>
-        </is>
-      </c>
-      <c r="G2" t="n">
-        <v>15</v>
-      </c>
-      <c r="H2" t="n">
-        <v>17</v>
-      </c>
-      <c r="I2" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
-      <c r="K2" t="n">
-        <v>9</v>
-      </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>44.4%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="M2" t="n">
         <v>1</v>
       </c>
       <c r="N2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -2915,7 +3089,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I6"/>
+  <dimension ref="A1:I7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -2979,64 +3153,64 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="C2" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="D2" t="n">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>59.3%</t>
+          <t>32.5%</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>37.5%</t>
+          <t>30.3%</t>
         </is>
       </c>
       <c r="H2" t="n">
         <v>1</v>
       </c>
       <c r="I2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Paint Non-RA</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="C3" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="D3" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>38.5%</t>
+          <t>52.6%</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>36.1%</t>
+          <t>28.8%</t>
         </is>
       </c>
       <c r="H3" t="n">
@@ -3049,36 +3223,36 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>9</v>
+        <v>32</v>
       </c>
       <c r="C4" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="D4" t="n">
-        <v>8</v>
+        <v>40</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>44.4%</t>
+          <t>62.5%</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>0.9</v>
+        <v>1.2</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>24.2%</t>
         </is>
       </c>
       <c r="H4" t="n">
         <v>3</v>
       </c>
       <c r="I4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -3088,32 +3262,32 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="C5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D5" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.2</v>
+        <v>0.7</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>6.9%</t>
+          <t>9.1%</t>
         </is>
       </c>
       <c r="H5" t="n">
         <v>4</v>
       </c>
       <c r="I5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
@@ -3123,7 +3297,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C6" t="n">
         <v>2</v>
@@ -3133,26 +3307,61 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>28.6%</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.2</v>
+        <v>0.9</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>6.9%</t>
+          <t>5.3%</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I6" t="n">
-        <v>4</v>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Corner 3 Right</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>3</v>
+      </c>
+      <c r="C7" t="n">
+        <v>3</v>
+      </c>
+      <c r="D7" t="n">
+        <v>9</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>3</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>2.3%</t>
+        </is>
+      </c>
+      <c r="H7" t="n">
+        <v>6</v>
+      </c>
+      <c r="I7" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I6"/>
+  <autoFilter ref="A1:I7"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3174,7 +3383,7 @@
     <col width="19" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
     <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="17" customWidth="1" min="9" max="9"/>
+    <col width="19" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
     <col width="16" customWidth="1" min="12" max="12"/>
@@ -3283,11 +3492,11 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>44.4%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -3296,44 +3505,44 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Paint Non-RA</t>
         </is>
       </c>
       <c r="J2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="L2" t="n">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>42.3%</t>
         </is>
       </c>
       <c r="N2" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>41.7%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="P2" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="3">
@@ -3362,15 +3571,15 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mid-Range</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -3379,42 +3588,42 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="L3" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>46.2%</t>
+          <t>36.4%</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="P3" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>CAQ_D._BACCHUS</t>
+          <t>CAQ_J._SHOATS</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>D. Bacchus</t>
+          <t>J. Shoats</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -3423,45 +3632,45 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>7</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>85.7%</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
           <t>Above the Break 3</t>
         </is>
       </c>
-      <c r="G4" t="n">
+      <c r="J4" t="n">
         <v>4</v>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>50.0%</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>Paint Non-RA</t>
-        </is>
-      </c>
-      <c r="J4" t="n">
-        <v>1</v>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
       <c r="L4" t="n">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>41.7%</t>
+          <t>81.0%</t>
         </is>
       </c>
       <c r="N4" t="n">
@@ -3473,163 +3682,163 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>1</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>CAQ_J._SHOATS</t>
+          <t>CAQ_D._BACCHUS</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>J. Shoats</t>
+          <t>D. Bacchus</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>7</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>85.7%</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
           <t>Restricted Area</t>
         </is>
       </c>
-      <c r="D5" t="n">
+      <c r="G5" t="n">
+        <v>7</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>28.6%</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="J5" t="n">
         <v>6</v>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
-      <c r="G5" t="n">
-        <v>3</v>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>66.7%</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>Mid-Range</t>
-        </is>
-      </c>
-      <c r="J5" t="n">
-        <v>2</v>
-      </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="L5" t="n">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>90.9%</t>
+          <t>47.6%</t>
         </is>
       </c>
       <c r="N5" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="P5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>CAQ_D._RIDGNAL</t>
+          <t>CAQ_D._HORTA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>D. Ridgnal</t>
+          <t>D. Horta</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="D6" t="n">
+        <v>7</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>28.6%</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>4</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>25.0%</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Mid-Range</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
         <v>2</v>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Paint Non-RA</t>
-        </is>
-      </c>
-      <c r="G6" t="n">
-        <v>2</v>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>50.0%</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>Corner 3 Left</t>
-        </is>
-      </c>
-      <c r="J6" t="n">
-        <v>1</v>
-      </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="L6" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>23.1%</t>
         </is>
       </c>
       <c r="N6" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>28.6%</t>
         </is>
       </c>
       <c r="P6" t="n">
-        <v>1.5</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>CAQ_D._HORTA</t>
+          <t>CAQ_I._PAVICEVIC</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>D. Horta</t>
+          <t>I. Pavicevic</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Paint Non-RA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -3637,54 +3846,64 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>60.0%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
+          <t>60.0%</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="J7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
       <c r="L7" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>63.6%</t>
         </is>
       </c>
       <c r="N7" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="P7" t="n">
-        <v>0.5</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>CAQ_I._PAVICEVIC</t>
+          <t>CAQ_D._RIDGNAL</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>I. Pavicevic</t>
+          <t>D. Ridgnal</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -3697,53 +3916,53 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>2</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
+        <v>2</v>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="L8" t="n">
+        <v>9</v>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>55.6%</t>
+        </is>
+      </c>
+      <c r="N8" t="n">
+        <v>3</v>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
           <t>33.3%</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
-      <c r="G8" t="n">
-        <v>1</v>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>Paint Non-RA</t>
-        </is>
-      </c>
-      <c r="J8" t="n">
-        <v>1</v>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="L8" t="n">
-        <v>5</v>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>60.0%</t>
-        </is>
-      </c>
-      <c r="N8" t="n">
-        <v>1</v>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
       <c r="P8" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="9">
@@ -3759,45 +3978,45 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>3</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
           <t>Above the Break 3</t>
         </is>
       </c>
-      <c r="D9" t="n">
-        <v>1</v>
-      </c>
-      <c r="E9" t="inlineStr">
+      <c r="G9" t="n">
+        <v>1</v>
+      </c>
+      <c r="H9" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Paint Non-RA</t>
-        </is>
-      </c>
-      <c r="G9" t="n">
-        <v>1</v>
-      </c>
-      <c r="H9" t="inlineStr">
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Mid-Range</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
+        <v>1</v>
+      </c>
+      <c r="K9" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>Restricted Area</t>
-        </is>
-      </c>
-      <c r="J9" t="n">
-        <v>1</v>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
       <c r="L9" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -3829,37 +4048,61 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
+          <t>Mid-Range</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>1</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>1</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
           <t>Paint Non-RA</t>
         </is>
       </c>
-      <c r="D10" t="n">
-        <v>1</v>
-      </c>
-      <c r="E10" t="inlineStr">
+      <c r="J10" t="n">
+        <v>1</v>
+      </c>
+      <c r="K10" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
       <c r="L10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="N10" t="n">
+        <v>1</v>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
           <t>0.0%</t>
         </is>
       </c>
-      <c r="N10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" t="inlineStr"/>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>0.7</v>
       </c>
     </row>
   </sheetData>
@@ -3874,11 +4117,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K6"/>
+  <dimension ref="A1:K13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
     <col width="19" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
@@ -3964,25 +4207,25 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F2" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>44.4%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>46.2%</t>
         </is>
       </c>
       <c r="J2" t="n">
@@ -4009,13 +4252,13 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F3" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -4027,7 +4270,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>54.5%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="J3" t="n">
@@ -4040,39 +4283,39 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>CAQ_J._THOMAS</t>
+          <t>CAQ_D._BACCHUS</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>J. Thomas</t>
+          <t>D. Bacchus</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Paint Non-RA</t>
         </is>
       </c>
       <c r="D4" t="n">
+        <v>7</v>
+      </c>
+      <c r="E4" t="n">
         <v>6</v>
       </c>
-      <c r="E4" t="n">
-        <v>4</v>
-      </c>
       <c r="F4" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>85.7%</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>1.3</v>
+        <v>1.7</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>46.2%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="J4" t="n">
@@ -4085,76 +4328,76 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>CAQ_D._BACCHUS</t>
+          <t>CAQ_J._SHOATS</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>D. Bacchus</t>
+          <t>J. Shoats</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Paint Non-RA</t>
         </is>
       </c>
       <c r="D5" t="n">
+        <v>7</v>
+      </c>
+      <c r="E5" t="n">
         <v>6</v>
       </c>
-      <c r="E5" t="n">
+      <c r="F5" t="n">
+        <v>12</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>85.7%</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="J5" t="n">
+        <v>1</v>
+      </c>
+      <c r="K5" t="n">
         <v>2</v>
-      </c>
-      <c r="F5" t="n">
-        <v>4</v>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>33.3%</t>
-        </is>
-      </c>
-      <c r="H5" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>50.0%</t>
-        </is>
-      </c>
-      <c r="J5" t="n">
-        <v>1</v>
-      </c>
-      <c r="K5" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>CAQ_D._HORTA</t>
+          <t>CAQ_D._BACCHUS</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>D. Horta</t>
+          <t>D. Bacchus</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>28.6%</t>
         </is>
       </c>
       <c r="H6" t="n">
@@ -4162,18 +4405,333 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>83.3%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="J6" t="n">
         <v>1</v>
       </c>
       <c r="K6" t="n">
-        <v>1</v>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>CAQ_D._HORTA</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>D. Horta</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>7</v>
+      </c>
+      <c r="E7" t="n">
+        <v>2</v>
+      </c>
+      <c r="F7" t="n">
+        <v>6</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>28.6%</t>
+        </is>
+      </c>
+      <c r="H7" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>53.8%</t>
+        </is>
+      </c>
+      <c r="J7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K7" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>CAQ_J._THOMAS</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>J. Thomas</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>6</v>
+      </c>
+      <c r="E8" t="n">
+        <v>4</v>
+      </c>
+      <c r="F8" t="n">
+        <v>8</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>66.7%</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>27.3%</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
+        <v>1</v>
+      </c>
+      <c r="K8" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>CAQ_D._BACCHUS</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>D. Bacchus</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>6</v>
+      </c>
+      <c r="E9" t="n">
+        <v>2</v>
+      </c>
+      <c r="F9" t="n">
+        <v>6</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
+        <v>1</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>28.6%</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
+        <v>3</v>
+      </c>
+      <c r="K9" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>CAQ_J._THOMAS</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>J. Thomas</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>6</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>27.3%</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
+        <v>1</v>
+      </c>
+      <c r="K10" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>CAQ_I._PAVICEVIC</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>I. Pavicevic</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>5</v>
+      </c>
+      <c r="E11" t="n">
+        <v>3</v>
+      </c>
+      <c r="F11" t="n">
+        <v>6</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>60.0%</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>45.5%</t>
+        </is>
+      </c>
+      <c r="J11" t="n">
+        <v>1</v>
+      </c>
+      <c r="K11" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>CAQ_I._PAVICEVIC</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>I. Pavicevic</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>5</v>
+      </c>
+      <c r="E12" t="n">
+        <v>3</v>
+      </c>
+      <c r="F12" t="n">
+        <v>6</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>60.0%</t>
+        </is>
+      </c>
+      <c r="H12" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>45.5%</t>
+        </is>
+      </c>
+      <c r="J12" t="n">
+        <v>1</v>
+      </c>
+      <c r="K12" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>CAQ_J._THOMAS</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>J. Thomas</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>5</v>
+      </c>
+      <c r="E13" t="n">
+        <v>2</v>
+      </c>
+      <c r="F13" t="n">
+        <v>4</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>40.0%</t>
+        </is>
+      </c>
+      <c r="H13" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>22.7%</t>
+        </is>
+      </c>
+      <c r="J13" t="n">
+        <v>3</v>
+      </c>
+      <c r="K13" t="n">
+        <v>2</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K6"/>
+  <autoFilter ref="A1:K13"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/site/leagues/betclic/2026_2027/xlsx/shot_packs/shot_pack_CAQ.xlsx
+++ b/site/leagues/betclic/2026_2027/xlsx/shot_packs/shot_pack_CAQ.xlsx
@@ -21,14 +21,14 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'overview'!$A$1:$W$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'alerts'!$A$1:$B$6</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'players_volume'!$A$1:$S$10</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'players_eff'!$A$1:$S$7</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'players_3pt_volume'!$A$1:$N$10</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'players_3pt_pct'!$A$1:$N$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'players_volume'!$A$1:$S$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'players_eff'!$A$1:$S$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'players_3pt_volume'!$A$1:$N$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'players_3pt_pct'!$A$1:$N$5</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'team_zones'!$A$1:$I$7</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'preferred_areas'!$A$1:$P$10</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'player_zones_volume'!$A$1:$K$13</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'player_zones_pct'!$A$1:$K$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'preferred_areas'!$A$1:$P$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'player_zones_volume'!$A$1:$K$21</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'player_zones_pct'!$A$1:$K$10</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -451,7 +451,7 @@
     <col width="19" customWidth="1" min="13" max="13"/>
     <col width="16" customWidth="1" min="14" max="14"/>
     <col width="16" customWidth="1" min="15" max="15"/>
-    <col width="14" customWidth="1" min="16" max="16"/>
+    <col width="17" customWidth="1" min="16" max="16"/>
     <col width="16" customWidth="1" min="17" max="17"/>
     <col width="16" customWidth="1" min="18" max="18"/>
     <col width="25" customWidth="1" min="19" max="19"/>
@@ -590,42 +590,42 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>132</v>
+        <v>204</v>
       </c>
       <c r="D2" t="n">
-        <v>62</v>
+        <v>88</v>
       </c>
       <c r="E2" t="n">
-        <v>142</v>
+        <v>200</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>47.0%</t>
+          <t>43.1%</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>82</v>
+        <v>128</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>53.7%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>50</v>
+        <v>76</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>36.0%</t>
+          <t>31.6%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>37.9%</t>
+          <t>37.3%</t>
         </is>
       </c>
       <c r="L2" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -633,40 +633,40 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>40</v>
+        <v>61</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>32.5%</t>
+          <t>27.9%</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>38</v>
+        <v>55</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>52.6%</t>
+          <t>60.0%</t>
         </is>
       </c>
       <c r="S2" t="n">
         <v>12</v>
       </c>
       <c r="T2" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="U2" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="V2" t="n">
         <v>12</v>
       </c>
       <c r="W2" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -681,10 +681,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K2"/>
+  <dimension ref="A1:K10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="1" max="1"/>
     <col width="13" customWidth="1" min="2" max="2"/>
     <col width="19" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
@@ -757,50 +757,410 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>CAQ_J._SHOATS</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>J. Shoats</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>9</v>
+      </c>
+      <c r="E2" t="n">
+        <v>7</v>
+      </c>
+      <c r="F2" t="n">
+        <v>14</v>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>77.8%</t>
+        </is>
+      </c>
+      <c r="H2" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>25.7%</t>
+        </is>
+      </c>
+      <c r="J2" t="n">
+        <v>2</v>
+      </c>
+      <c r="K2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>CAQ_J._SHOATS</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>J. Shoats</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>13</v>
+      </c>
+      <c r="E3" t="n">
+        <v>10</v>
+      </c>
+      <c r="F3" t="n">
+        <v>20</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>76.9%</t>
+        </is>
+      </c>
+      <c r="H3" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>37.1%</t>
+        </is>
+      </c>
+      <c r="J3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K3" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>CAQ_D._BACCHUS</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>D. Bacchus</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>9</v>
+      </c>
+      <c r="E4" t="n">
+        <v>6</v>
+      </c>
+      <c r="F4" t="n">
+        <v>12</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>66.7%</t>
+        </is>
+      </c>
+      <c r="H4" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="J4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>CAQ_J._THOMAS</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>J. Thomas</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>11</v>
+      </c>
+      <c r="E5" t="n">
+        <v>6</v>
+      </c>
+      <c r="F5" t="n">
+        <v>12</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>54.5%</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="J5" t="n">
+        <v>1</v>
+      </c>
+      <c r="K5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>CAQ_J._SHOATS</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>J. Shoats</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Mid-Range</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>8</v>
+      </c>
+      <c r="E6" t="n">
+        <v>4</v>
+      </c>
+      <c r="F6" t="n">
+        <v>8</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>22.9%</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
+        <v>3</v>
+      </c>
+      <c r="K6" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
           <t>CAQ_A._THIAM</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>A. Thiam</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>Above the Break 3</t>
         </is>
       </c>
-      <c r="D2" t="n">
-        <v>12</v>
-      </c>
-      <c r="E2" t="n">
-        <v>6</v>
-      </c>
-      <c r="F2" t="n">
-        <v>18</v>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>50.0%</t>
-        </is>
-      </c>
-      <c r="H2" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>46.2%</t>
-        </is>
-      </c>
-      <c r="J2" t="n">
-        <v>1</v>
-      </c>
-      <c r="K2" t="n">
-        <v>1</v>
+      <c r="D7" t="n">
+        <v>15</v>
+      </c>
+      <c r="E7" t="n">
+        <v>7</v>
+      </c>
+      <c r="F7" t="n">
+        <v>21</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>46.7%</t>
+        </is>
+      </c>
+      <c r="H7" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>40.5%</t>
+        </is>
+      </c>
+      <c r="J7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K7" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>CAQ_D._BACCHUS</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>D. Bacchus</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>9</v>
+      </c>
+      <c r="E8" t="n">
+        <v>3</v>
+      </c>
+      <c r="F8" t="n">
+        <v>9</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
+        <v>1</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
+        <v>1</v>
+      </c>
+      <c r="K8" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>CAQ_D._HORTA</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>D. Horta</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>10</v>
+      </c>
+      <c r="E9" t="n">
+        <v>3</v>
+      </c>
+      <c r="F9" t="n">
+        <v>9</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>30.0%</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>47.6%</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
+        <v>1</v>
+      </c>
+      <c r="K9" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>CAQ_J._THOMAS</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>J. Thomas</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>8</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>24.2%</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
+        <v>2</v>
+      </c>
+      <c r="K10" t="n">
+        <v>3</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K2"/>
+  <autoFilter ref="A1:K10"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -838,7 +1198,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Maior volume: A. Thiam (26 L)</t>
+          <t>Maior volume: A. Thiam (37 L)</t>
         </is>
       </c>
     </row>
@@ -850,7 +1210,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Maior volume 3pt: A. Thiam (18 3PA)</t>
+          <t>Maior volume 3pt: A. Thiam (24 3PA)</t>
         </is>
       </c>
     </row>
@@ -862,7 +1222,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Mais eficaz: J. Shoats (1.7 pts/shot)</t>
+          <t>Mais eficaz: J. Shoats (1.4 pts/shot)</t>
         </is>
       </c>
     </row>
@@ -874,7 +1234,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Zona mais usada: Above the Break 3 (40 L)</t>
+          <t>Zona mais usada: Above the Break 3 (61 L)</t>
         </is>
       </c>
     </row>
@@ -886,7 +1246,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Zona mais eficaz: Restricted Area (62.5%)</t>
+          <t>Zona mais eficaz: Restricted Area (60.0%)</t>
         </is>
       </c>
     </row>
@@ -902,7 +1262,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S10"/>
+  <dimension ref="A1:S11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1035,21 +1395,21 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="D2" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="E2" t="n">
-        <v>31</v>
+        <v>44</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>42.3%</t>
+          <t>43.2%</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -1058,7 +1418,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>69.2%</t>
+          <t>64.9%</t>
         </is>
       </c>
       <c r="J2" t="n">
@@ -1070,11 +1430,11 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>46.7%</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -1083,11 +1443,11 @@
         </is>
       </c>
       <c r="O2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="Q2" t="n">
@@ -1103,120 +1463,120 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>CAQ_J._THOMAS</t>
+          <t>CAQ_J._SHOATS</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>J. Thomas</t>
+          <t>J. Shoats</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>22</v>
+        <v>35</v>
       </c>
       <c r="D3" t="n">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="E3" t="n">
-        <v>17</v>
+        <v>48</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>36.4%</t>
+          <t>65.7%</t>
         </is>
       </c>
       <c r="G3" t="n">
+        <v>5</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>40.0%</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>14.3%</t>
+        </is>
+      </c>
+      <c r="J3" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="L3" t="n">
+        <v>13</v>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>76.9%</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="O3" t="n">
         <v>9</v>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>11.1%</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>40.9%</t>
-        </is>
-      </c>
-      <c r="J3" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>Restricted Area</t>
-        </is>
-      </c>
-      <c r="L3" t="n">
-        <v>6</v>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>66.7%</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
-      <c r="O3" t="n">
-        <v>6</v>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>77.8%</t>
         </is>
       </c>
       <c r="Q3" t="n">
         <v>2</v>
       </c>
       <c r="R3" t="n">
+        <v>1</v>
+      </c>
+      <c r="S3" t="n">
         <v>5</v>
-      </c>
-      <c r="S3" t="n">
-        <v>2</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>CAQ_J._SHOATS</t>
+          <t>CAQ_J._THOMAS</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>J. Shoats</t>
+          <t>J. Thomas</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>21</v>
+        <v>33</v>
       </c>
       <c r="D4" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="E4" t="n">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>81.0%</t>
+          <t>39.4%</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>8.3%</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>19.0%</t>
+          <t>36.4%</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>1.7</v>
+        <v>0.8</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -1224,34 +1584,34 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>54.5%</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="O4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>85.7%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="Q4" t="n">
         <v>3</v>
       </c>
       <c r="R4" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5">
@@ -1266,69 +1626,69 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="D5" t="n">
+        <v>11</v>
+      </c>
+      <c r="E5" t="n">
+        <v>25</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>40.7%</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
         <v>10</v>
       </c>
-      <c r="E5" t="n">
-        <v>22</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>47.6%</t>
-        </is>
-      </c>
-      <c r="G5" t="n">
-        <v>6</v>
-      </c>
       <c r="H5" t="inlineStr">
         <is>
+          <t>30.0%</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>37.0%</t>
+        </is>
+      </c>
+      <c r="J5" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="L5" t="n">
+        <v>9</v>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>66.7%</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="O5" t="n">
+        <v>9</v>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
           <t>33.3%</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>28.6%</t>
-        </is>
-      </c>
-      <c r="J5" t="n">
-        <v>1</v>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>Paint Non-RA</t>
-        </is>
-      </c>
-      <c r="L5" t="n">
-        <v>7</v>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>85.7%</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>Restricted Area</t>
-        </is>
-      </c>
-      <c r="O5" t="n">
-        <v>7</v>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>28.6%</t>
-        </is>
-      </c>
       <c r="Q5" t="n">
+        <v>4</v>
+      </c>
+      <c r="R5" t="n">
+        <v>5</v>
+      </c>
+      <c r="S5" t="n">
         <v>3</v>
-      </c>
-      <c r="R5" t="n">
-        <v>4</v>
-      </c>
-      <c r="S5" t="n">
-        <v>4</v>
       </c>
     </row>
     <row r="6">
@@ -1343,34 +1703,34 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="D6" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E6" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>23.1%</t>
+          <t>28.6%</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>28.6%</t>
+          <t>30.0%</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>53.8%</t>
+          <t>47.6%</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -1378,11 +1738,11 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>28.6%</t>
+          <t>30.0%</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1391,18 +1751,18 @@
         </is>
       </c>
       <c r="O6" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="Q6" t="n">
         <v>5</v>
       </c>
       <c r="R6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="S6" t="n">
         <v>3</v>
@@ -1411,60 +1771,60 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>CAQ_I._PAVICEVIC</t>
+          <t>CAQ_A._HALLMAN</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>I. Pavicevic</t>
+          <t>A. Hallman</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="D7" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E7" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>63.6%</t>
+          <t>17.6%</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>9.1%</t>
+          <t>29.4%</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>1.4</v>
+        <v>0.4</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="L7" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="O7" t="n">
@@ -1472,55 +1832,55 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="Q7" t="n">
         <v>6</v>
       </c>
       <c r="R7" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="S7" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>CAQ_D._RIDGNAL</t>
+          <t>CAQ_I._PAVICEVIC</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>D. Ridgnal</t>
+          <t>I. Pavicevic</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="D8" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E8" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>55.6%</t>
+          <t>57.1%</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>14.3%</t>
         </is>
       </c>
       <c r="J8" t="n">
@@ -1532,11 +1892,11 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1545,75 +1905,75 @@
         </is>
       </c>
       <c r="O8" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>60.0%</t>
         </is>
       </c>
       <c r="Q8" t="n">
         <v>7</v>
       </c>
       <c r="R8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S8" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>CAQ_A._HALLMAN</t>
+          <t>CAQ_D._RIDGNAL</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>A. Hallman</t>
+          <t>D. Ridgnal</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>35.7%</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="L9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1622,21 +1982,21 @@
         </is>
       </c>
       <c r="O9" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="R9" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="S9" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10">
@@ -1651,7 +2011,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D10" t="n">
         <v>1</v>
@@ -1661,7 +2021,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1674,11 +2034,11 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -1686,11 +2046,11 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1710,14 +2070,81 @@
         <v>9</v>
       </c>
       <c r="R10" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="S10" t="n">
-        <v>7</v>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>CAQ_J._SILVA</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>J. Silva</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>2</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="G11" t="n">
+        <v>2</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="L11" t="n">
+        <v>2</v>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="n">
+        <v>10</v>
+      </c>
+      <c r="R11" t="n">
+        <v>10</v>
+      </c>
+      <c r="S11" t="n">
+        <v>8</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:S10"/>
+  <autoFilter ref="A1:S11"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1728,7 +2155,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S7"/>
+  <dimension ref="A1:S9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1861,33 +2288,33 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1.7</v>
+        <v>1.4</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>81.0%</t>
+          <t>65.7%</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>21</v>
+        <v>35</v>
       </c>
       <c r="F2" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="G2" t="n">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="H2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>19.0%</t>
+          <t>14.3%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -1896,11 +2323,11 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>76.9%</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -1909,21 +2336,21 @@
         </is>
       </c>
       <c r="O2" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>85.7%</t>
+          <t>77.8%</t>
         </is>
       </c>
       <c r="Q2" t="n">
         <v>1</v>
       </c>
       <c r="R2" t="n">
+        <v>2</v>
+      </c>
+      <c r="S2" t="n">
         <v>3</v>
-      </c>
-      <c r="S2" t="n">
-        <v>2</v>
       </c>
     </row>
     <row r="3">
@@ -1938,51 +2365,51 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>63.6%</t>
+          <t>57.1%</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G3" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>9.1%</t>
+          <t>14.3%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="L3" t="n">
+        <v>6</v>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>66.7%</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
           <t>Paint Non-RA</t>
-        </is>
-      </c>
-      <c r="L3" t="n">
-        <v>5</v>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>60.0%</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>Restricted Area</t>
         </is>
       </c>
       <c r="O3" t="n">
@@ -1997,7 +2424,7 @@
         <v>2</v>
       </c>
       <c r="R3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -2019,20 +2446,20 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>42.3%</t>
+          <t>43.2%</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="F4" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="G4" t="n">
-        <v>31</v>
+        <v>44</v>
       </c>
       <c r="H4" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -2041,7 +2468,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>69.2%</t>
+          <t>64.9%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -2050,11 +2477,11 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>46.7%</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -2063,11 +2490,11 @@
         </is>
       </c>
       <c r="O4" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="Q4" t="n">
@@ -2077,135 +2504,135 @@
         <v>1</v>
       </c>
       <c r="S4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>CAQ_D._BACCHUS</t>
+          <t>CAQ_D._RIDGNAL</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>D. Bacchus</t>
+          <t>D. Ridgnal</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>47.6%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="F5" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G5" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="H5" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>28.6%</t>
+          <t>35.7%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="L5" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>85.7%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="O5" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>28.6%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="Q5" t="n">
         <v>4</v>
       </c>
       <c r="R5" t="n">
+        <v>7</v>
+      </c>
+      <c r="S5" t="n">
         <v>3</v>
-      </c>
-      <c r="S5" t="n">
-        <v>4</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>CAQ_J._THOMAS</t>
+          <t>CAQ_D._BACCHUS</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>J. Thomas</t>
+          <t>D. Bacchus</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>36.4%</t>
+          <t>40.7%</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="F6" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="G6" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="H6" t="n">
+        <v>10</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>30.0%</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>37.0%</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="L6" t="n">
         <v>9</v>
       </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>11.1%</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>40.9%</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>Restricted Area</t>
-        </is>
-      </c>
-      <c r="L6" t="n">
-        <v>6</v>
-      </c>
       <c r="M6" t="inlineStr">
         <is>
           <t>66.7%</t>
@@ -2217,102 +2644,256 @@
         </is>
       </c>
       <c r="O6" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="Q6" t="n">
         <v>5</v>
       </c>
       <c r="R6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="S6" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>CAQ_D._HORTA</t>
+          <t>CAQ_J._THOMAS</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>D. Horta</t>
+          <t>J. Thomas</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>23.1%</t>
+          <t>39.4%</t>
         </is>
       </c>
       <c r="E7" t="n">
+        <v>33</v>
+      </c>
+      <c r="F7" t="n">
         <v>13</v>
       </c>
-      <c r="F7" t="n">
-        <v>3</v>
-      </c>
       <c r="G7" t="n">
+        <v>27</v>
+      </c>
+      <c r="H7" t="n">
+        <v>12</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>8.3%</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>36.4%</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="L7" t="n">
+        <v>11</v>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>54.5%</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="O7" t="n">
         <v>8</v>
       </c>
-      <c r="H7" t="n">
-        <v>7</v>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>28.6%</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>53.8%</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
-      <c r="L7" t="n">
-        <v>7</v>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>28.6%</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>Paint Non-RA</t>
-        </is>
-      </c>
-      <c r="O7" t="n">
-        <v>4</v>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="Q7" t="n">
         <v>6</v>
       </c>
       <c r="R7" t="n">
+        <v>3</v>
+      </c>
+      <c r="S7" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>CAQ_D._HORTA</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>D. Horta</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>28.6%</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>21</v>
+      </c>
+      <c r="F8" t="n">
+        <v>6</v>
+      </c>
+      <c r="G8" t="n">
+        <v>15</v>
+      </c>
+      <c r="H8" t="n">
+        <v>10</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>30.0%</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>47.6%</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="L8" t="n">
+        <v>10</v>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>30.0%</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="O8" t="n">
+        <v>6</v>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>16.7%</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>7</v>
+      </c>
+      <c r="R8" t="n">
         <v>5</v>
       </c>
-      <c r="S7" t="n">
+      <c r="S8" t="n">
         <v>5</v>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>CAQ_A._HALLMAN</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>A. Hallman</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>17.6%</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>17</v>
+      </c>
+      <c r="F9" t="n">
+        <v>3</v>
+      </c>
+      <c r="G9" t="n">
+        <v>6</v>
+      </c>
+      <c r="H9" t="n">
+        <v>5</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>29.4%</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="L9" t="n">
+        <v>6</v>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="O9" t="n">
+        <v>5</v>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>8</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6</v>
+      </c>
+      <c r="S9" t="n">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:S7"/>
+  <autoFilter ref="A1:S9"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2323,7 +2904,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N10"/>
+  <dimension ref="A1:N11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -2426,10 +3007,10 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="D2" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -2438,14 +3019,14 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>69.2%</t>
+          <t>64.9%</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="H2" t="n">
-        <v>31</v>
+        <v>44</v>
       </c>
       <c r="I2" t="n">
         <v>1.2</v>
@@ -2456,18 +3037,18 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>46.7%</t>
         </is>
       </c>
       <c r="M2" t="n">
         <v>1</v>
       </c>
       <c r="N2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -2482,26 +3063,26 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D3" t="n">
         <v>1</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>8.3%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>40.9%</t>
+          <t>36.4%</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="H3" t="n">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="I3" t="n">
         <v>0.8</v>
@@ -2512,67 +3093,67 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>54.5%</t>
         </is>
       </c>
       <c r="M3" t="n">
         <v>2</v>
       </c>
       <c r="N3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>CAQ_D._HORTA</t>
+          <t>CAQ_D._BACCHUS</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>D. Horta</t>
+          <t>D. Bacchus</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>28.6%</t>
+          <t>30.0%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>53.8%</t>
+          <t>37.0%</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="H4" t="n">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="I4" t="n">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Paint Non-RA</t>
         </is>
       </c>
       <c r="K4" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>28.6%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="M4" t="n">
@@ -2585,57 +3166,57 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>CAQ_D._BACCHUS</t>
+          <t>CAQ_D._HORTA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>D. Bacchus</t>
+          <t>D. Horta</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>30.0%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>28.6%</t>
+          <t>47.6%</t>
         </is>
       </c>
       <c r="G5" t="n">
         <v>21</v>
       </c>
       <c r="H5" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="I5" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="K5" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>85.7%</t>
+          <t>30.0%</t>
         </is>
       </c>
       <c r="M5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6">
@@ -2650,29 +3231,29 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D6" t="n">
         <v>2</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>19.0%</t>
+          <t>14.3%</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>21</v>
+        <v>35</v>
       </c>
       <c r="H6" t="n">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="I6" t="n">
-        <v>1.7</v>
+        <v>1.4</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -2680,18 +3261,18 @@
         </is>
       </c>
       <c r="K6" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>76.9%</t>
         </is>
       </c>
       <c r="M6" t="n">
         <v>5</v>
       </c>
       <c r="N6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7">
@@ -2706,175 +3287,175 @@
         </is>
       </c>
       <c r="C7" t="n">
+        <v>5</v>
+      </c>
+      <c r="D7" t="n">
+        <v>2</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>40.0%</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>35.7%</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>14</v>
+      </c>
+      <c r="H7" t="n">
+        <v>16</v>
+      </c>
+      <c r="I7" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="K7" t="n">
+        <v>4</v>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="M7" t="n">
+        <v>5</v>
+      </c>
+      <c r="N7" t="n">
         <v>3</v>
-      </c>
-      <c r="D7" t="n">
-        <v>1</v>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>33.3%</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>33.3%</t>
-        </is>
-      </c>
-      <c r="G7" t="n">
-        <v>9</v>
-      </c>
-      <c r="H7" t="n">
-        <v>11</v>
-      </c>
-      <c r="I7" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>Restricted Area</t>
-        </is>
-      </c>
-      <c r="K7" t="n">
-        <v>3</v>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="M7" t="n">
-        <v>6</v>
-      </c>
-      <c r="N7" t="n">
-        <v>4</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>CAQ_I._PAVICEVIC</t>
+          <t>CAQ_A._HALLMAN</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>I. Pavicevic</t>
+          <t>A. Hallman</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>9.1%</t>
+          <t>29.4%</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="H8" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="I8" t="n">
-        <v>1.4</v>
+        <v>0.4</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="K8" t="n">
+        <v>6</v>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="M8" t="n">
         <v>5</v>
       </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>60.0%</t>
-        </is>
-      </c>
-      <c r="M8" t="n">
-        <v>7</v>
-      </c>
       <c r="N8" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>CAQ_A._HALLMAN</t>
+          <t>CAQ_I._PAVICEVIC</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>A. Hallman</t>
+          <t>I. Pavicevic</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>14.3%</t>
         </is>
       </c>
       <c r="G9" t="n">
+        <v>14</v>
+      </c>
+      <c r="H9" t="n">
+        <v>17</v>
+      </c>
+      <c r="I9" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="K9" t="n">
         <v>6</v>
       </c>
-      <c r="H9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>Paint Non-RA</t>
-        </is>
-      </c>
-      <c r="K9" t="n">
-        <v>3</v>
-      </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="M9" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N9" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>CAQ_J._CARNEIRO</t>
+          <t>CAQ_J._SILVA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>J. Carneiro</t>
+          <t>J. Silva</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D10" t="n">
         <v>0</v>
@@ -2886,40 +3467,96 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="K10" t="n">
         <v>2</v>
       </c>
-      <c r="I10" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>Mid-Range</t>
-        </is>
-      </c>
-      <c r="K10" t="n">
-        <v>1</v>
-      </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="M10" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N10" t="n">
         <v>8</v>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>CAQ_J._CARNEIRO</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>J. Carneiro</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>1</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>25.0%</t>
+        </is>
+      </c>
+      <c r="G11" t="n">
+        <v>4</v>
+      </c>
+      <c r="H11" t="n">
+        <v>2</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Mid-Range</t>
+        </is>
+      </c>
+      <c r="K11" t="n">
+        <v>2</v>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="M11" t="n">
+        <v>10</v>
+      </c>
+      <c r="N11" t="n">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:N10"/>
+  <autoFilter ref="A1:N11"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2930,10 +3567,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N2"/>
+  <dimension ref="A1:N5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="1" max="1"/>
     <col width="13" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
@@ -3033,10 +3670,10 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="D2" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -3045,14 +3682,14 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>69.2%</t>
+          <t>64.9%</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="H2" t="n">
-        <v>31</v>
+        <v>44</v>
       </c>
       <c r="I2" t="n">
         <v>1.2</v>
@@ -3063,22 +3700,190 @@
         </is>
       </c>
       <c r="K2" t="n">
+        <v>15</v>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>46.7%</t>
+        </is>
+      </c>
+      <c r="M2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>CAQ_D._BACCHUS</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>D. Bacchus</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>10</v>
+      </c>
+      <c r="D3" t="n">
+        <v>3</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>30.0%</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>37.0%</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>27</v>
+      </c>
+      <c r="H3" t="n">
+        <v>25</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="K3" t="n">
+        <v>9</v>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>66.7%</t>
+        </is>
+      </c>
+      <c r="M3" t="n">
+        <v>3</v>
+      </c>
+      <c r="N3" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>CAQ_D._HORTA</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>D. Horta</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>10</v>
+      </c>
+      <c r="D4" t="n">
+        <v>3</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>30.0%</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>47.6%</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>21</v>
+      </c>
+      <c r="H4" t="n">
+        <v>15</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="K4" t="n">
+        <v>10</v>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>30.0%</t>
+        </is>
+      </c>
+      <c r="M4" t="n">
+        <v>3</v>
+      </c>
+      <c r="N4" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>CAQ_J._THOMAS</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>J. Thomas</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
         <v>12</v>
       </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>50.0%</t>
-        </is>
-      </c>
-      <c r="M2" t="n">
-        <v>1</v>
-      </c>
-      <c r="N2" t="n">
+      <c r="D5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>8.3%</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>36.4%</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>33</v>
+      </c>
+      <c r="H5" t="n">
+        <v>27</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="K5" t="n">
+        <v>11</v>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>54.5%</t>
+        </is>
+      </c>
+      <c r="M5" t="n">
         <v>2</v>
       </c>
+      <c r="N5" t="n">
+        <v>7</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N2"/>
+  <autoFilter ref="A1:N5"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3157,25 +3962,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>40</v>
+        <v>61</v>
       </c>
       <c r="C2" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="D2" t="n">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>32.5%</t>
+          <t>27.9%</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>30.3%</t>
+          <t>29.9%</t>
         </is>
       </c>
       <c r="H2" t="n">
@@ -3188,71 +3993,71 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>38</v>
+        <v>55</v>
       </c>
       <c r="C3" t="n">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="D3" t="n">
-        <v>40</v>
+        <v>66</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>52.6%</t>
+          <t>60.0%</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>28.8%</t>
+          <t>27.0%</t>
         </is>
       </c>
       <c r="H3" t="n">
         <v>2</v>
       </c>
       <c r="I3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Paint Non-RA</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="C4" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="D4" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>48.9%</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>24.2%</t>
+          <t>23.0%</t>
         </is>
       </c>
       <c r="H4" t="n">
         <v>3</v>
       </c>
       <c r="I4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5">
@@ -3262,25 +4067,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="C5" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D5" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>30.8%</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>9.1%</t>
+          <t>12.7%</t>
         </is>
       </c>
       <c r="H5" t="n">
@@ -3297,32 +4102,32 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D6" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>28.6%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>5.3%</t>
+          <t>4.4%</t>
         </is>
       </c>
       <c r="H6" t="n">
         <v>5</v>
       </c>
       <c r="I6" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7">
@@ -3332,25 +4137,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D7" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="H7" t="n">
@@ -3372,7 +4177,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P10"/>
+  <dimension ref="A1:P11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -3492,11 +4297,11 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>46.7%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -3505,11 +4310,11 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -3518,23 +4323,23 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="L2" t="n">
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>42.3%</t>
+          <t>43.2%</t>
         </is>
       </c>
       <c r="N2" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
@@ -3548,12 +4353,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>CAQ_J._THOMAS</t>
+          <t>CAQ_J._SHOATS</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>J. Thomas</t>
+          <t>J. Shoats</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -3562,68 +4367,68 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>76.9%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Paint Non-RA</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>77.8%</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Mid-Range</t>
         </is>
       </c>
       <c r="J3" t="n">
+        <v>8</v>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="L3" t="n">
+        <v>35</v>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>65.7%</t>
+        </is>
+      </c>
+      <c r="N3" t="n">
         <v>5</v>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t>40.0%</t>
         </is>
       </c>
-      <c r="L3" t="n">
-        <v>22</v>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>36.4%</t>
-        </is>
-      </c>
-      <c r="N3" t="n">
-        <v>9</v>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>11.1%</t>
-        </is>
-      </c>
       <c r="P3" t="n">
-        <v>0.8</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>CAQ_J._SHOATS</t>
+          <t>CAQ_J._THOMAS</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>J. Shoats</t>
+          <t>J. Thomas</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -3632,33 +4437,33 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>54.5%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>8</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
           <t>Paint Non-RA</t>
         </is>
       </c>
-      <c r="G4" t="n">
-        <v>7</v>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>85.7%</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
       <c r="J4" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -3666,23 +4471,23 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>21</v>
+        <v>33</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>81.0%</t>
+          <t>39.4%</t>
         </is>
       </c>
       <c r="N4" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>8.3%</t>
         </is>
       </c>
       <c r="P4" t="n">
-        <v>1.7</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="5">
@@ -3702,57 +4507,57 @@
         </is>
       </c>
       <c r="D5" t="n">
+        <v>9</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>66.7%</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>9</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="J5" t="n">
         <v>7</v>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>85.7%</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Restricted Area</t>
-        </is>
-      </c>
-      <c r="G5" t="n">
-        <v>7</v>
-      </c>
-      <c r="H5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>28.6%</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
-      <c r="J5" t="n">
-        <v>6</v>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>33.3%</t>
-        </is>
-      </c>
       <c r="L5" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>47.6%</t>
+          <t>40.7%</t>
         </is>
       </c>
       <c r="N5" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>30.0%</t>
         </is>
       </c>
       <c r="P5" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="6">
@@ -3772,86 +4577,86 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
+          <t>30.0%</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>6</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>16.7%</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
+        <v>3</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>66.7%</t>
+        </is>
+      </c>
+      <c r="L6" t="n">
+        <v>21</v>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
           <t>28.6%</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Paint Non-RA</t>
-        </is>
-      </c>
-      <c r="G6" t="n">
-        <v>4</v>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>25.0%</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>Mid-Range</t>
-        </is>
-      </c>
-      <c r="J6" t="n">
-        <v>2</v>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="L6" t="n">
-        <v>13</v>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>23.1%</t>
-        </is>
-      </c>
       <c r="N6" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>28.6%</t>
+          <t>30.0%</t>
         </is>
       </c>
       <c r="P6" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>CAQ_I._PAVICEVIC</t>
+          <t>CAQ_A._HALLMAN</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>I. Pavicevic</t>
+          <t>A. Hallman</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -3859,51 +4664,51 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Mid-Range</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="L7" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>63.6%</t>
+          <t>17.6%</t>
         </is>
       </c>
       <c r="N7" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="P7" t="n">
-        <v>1.4</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>CAQ_D._RIDGNAL</t>
+          <t>CAQ_I._PAVICEVIC</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>D. Ridgnal</t>
+          <t>I. Pavicevic</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -3912,11 +4717,11 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -3925,11 +4730,11 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>60.0%</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -3942,23 +4747,23 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="L8" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>55.6%</t>
+          <t>57.1%</t>
         </is>
       </c>
       <c r="N8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="P8" t="n">
@@ -3968,71 +4773,71 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>CAQ_A._HALLMAN</t>
+          <t>CAQ_D._RIDGNAL</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>A. Hallman</t>
+          <t>D. Ridgnal</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="D9" t="n">
+        <v>4</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>4</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>25.0%</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Mid-Range</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
         <v>3</v>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
-      <c r="G9" t="n">
-        <v>1</v>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>Mid-Range</t>
-        </is>
-      </c>
-      <c r="J9" t="n">
-        <v>1</v>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
       <c r="L9" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="N9" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="10">
@@ -4052,11 +4857,11 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -4086,11 +4891,11 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="N10" t="n">
@@ -4102,11 +4907,61 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>CAQ_J._SILVA</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>J. Silva</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>2</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="n">
+        <v>2</v>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="N11" t="n">
+        <v>2</v>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:P10"/>
+  <autoFilter ref="A1:P11"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4117,7 +4972,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K13"/>
+  <dimension ref="A1:K21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -4207,25 +5062,25 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F2" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>46.7%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>46.2%</t>
+          <t>40.5%</t>
         </is>
       </c>
       <c r="J2" t="n">
@@ -4252,52 +5107,52 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="E3" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F3" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>76.9%</t>
         </is>
       </c>
       <c r="H3" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>37.1%</t>
+        </is>
+      </c>
+      <c r="J3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K3" t="n">
         <v>2</v>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>33.3%</t>
-        </is>
-      </c>
-      <c r="J3" t="n">
-        <v>1</v>
-      </c>
-      <c r="K3" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>CAQ_D._BACCHUS</t>
+          <t>CAQ_J._THOMAS</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>D. Bacchus</t>
+          <t>J. Thomas</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E4" t="n">
         <v>6</v>
@@ -4307,11 +5162,11 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>85.7%</t>
+          <t>54.5%</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>1.7</v>
+        <v>1.1</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -4328,129 +5183,129 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>CAQ_J._SHOATS</t>
+          <t>CAQ_D._HORTA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>J. Shoats</t>
+          <t>D. Horta</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E5" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F5" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>85.7%</t>
+          <t>30.0%</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>1.7</v>
+        <v>0.9</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>47.6%</t>
         </is>
       </c>
       <c r="J5" t="n">
         <v>1</v>
       </c>
       <c r="K5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>CAQ_D._BACCHUS</t>
+          <t>CAQ_J._SHOATS</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>D. Bacchus</t>
+          <t>J. Shoats</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Paint Non-RA</t>
         </is>
       </c>
       <c r="D6" t="n">
+        <v>9</v>
+      </c>
+      <c r="E6" t="n">
         <v>7</v>
       </c>
-      <c r="E6" t="n">
+      <c r="F6" t="n">
+        <v>14</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>77.8%</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>25.7%</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
         <v>2</v>
       </c>
-      <c r="F6" t="n">
-        <v>4</v>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>28.6%</t>
-        </is>
-      </c>
-      <c r="H6" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>33.3%</t>
-        </is>
-      </c>
-      <c r="J6" t="n">
-        <v>1</v>
-      </c>
       <c r="K6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>CAQ_D._HORTA</t>
+          <t>CAQ_D._BACCHUS</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>D. Horta</t>
+          <t>D. Bacchus</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Paint Non-RA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E7" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F7" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>28.6%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>0.9</v>
+        <v>1.3</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>53.8%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="J7" t="n">
@@ -4463,76 +5318,76 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>CAQ_J._THOMAS</t>
+          <t>CAQ_D._BACCHUS</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>J. Thomas</t>
+          <t>D. Bacchus</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F8" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>27.3%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="J8" t="n">
         <v>1</v>
       </c>
       <c r="K8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>CAQ_D._BACCHUS</t>
+          <t>CAQ_J._SHOATS</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>D. Bacchus</t>
+          <t>J. Shoats</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Mid-Range</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E9" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F9" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="H9" t="n">
@@ -4540,14 +5395,14 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>28.6%</t>
+          <t>22.9%</t>
         </is>
       </c>
       <c r="J9" t="n">
         <v>3</v>
       </c>
       <c r="K9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10">
@@ -4567,7 +5422,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -4585,11 +5440,11 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>27.3%</t>
+          <t>24.2%</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K10" t="n">
         <v>3</v>
@@ -4598,46 +5453,46 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>CAQ_I._PAVICEVIC</t>
+          <t>CAQ_D._BACCHUS</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>I. Pavicevic</t>
+          <t>D. Bacchus</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E11" t="n">
+        <v>2</v>
+      </c>
+      <c r="F11" t="n">
+        <v>4</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>28.6%</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>25.9%</t>
+        </is>
+      </c>
+      <c r="J11" t="n">
         <v>3</v>
       </c>
-      <c r="F11" t="n">
-        <v>6</v>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>60.0%</t>
-        </is>
-      </c>
-      <c r="H11" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>45.5%</t>
-        </is>
-      </c>
-      <c r="J11" t="n">
-        <v>1</v>
-      </c>
       <c r="K11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="12">
@@ -4657,25 +5512,25 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F12" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>45.5%</t>
+          <t>42.9%</t>
         </is>
       </c>
       <c r="J12" t="n">
@@ -4688,50 +5543,410 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>CAQ_A._HALLMAN</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>A. Hallman</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>6</v>
+      </c>
+      <c r="E13" t="n">
+        <v>3</v>
+      </c>
+      <c r="F13" t="n">
+        <v>6</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="H13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>35.3%</t>
+        </is>
+      </c>
+      <c r="J13" t="n">
+        <v>1</v>
+      </c>
+      <c r="K13" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
           <t>CAQ_J._THOMAS</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>J. Thomas</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t>Paint Non-RA</t>
         </is>
       </c>
-      <c r="D13" t="n">
+      <c r="D14" t="n">
+        <v>6</v>
+      </c>
+      <c r="E14" t="n">
+        <v>3</v>
+      </c>
+      <c r="F14" t="n">
+        <v>6</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="H14" t="n">
+        <v>1</v>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>18.2%</t>
+        </is>
+      </c>
+      <c r="J14" t="n">
+        <v>3</v>
+      </c>
+      <c r="K14" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>CAQ_A._THIAM</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>A. Thiam</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Corner 3 Left</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>6</v>
+      </c>
+      <c r="E15" t="n">
+        <v>2</v>
+      </c>
+      <c r="F15" t="n">
+        <v>6</v>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="H15" t="n">
+        <v>1</v>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>16.2%</t>
+        </is>
+      </c>
+      <c r="J15" t="n">
+        <v>2</v>
+      </c>
+      <c r="K15" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>CAQ_A._THIAM</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>A. Thiam</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>6</v>
+      </c>
+      <c r="E16" t="n">
+        <v>2</v>
+      </c>
+      <c r="F16" t="n">
+        <v>4</v>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="H16" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>16.2%</t>
+        </is>
+      </c>
+      <c r="J16" t="n">
+        <v>2</v>
+      </c>
+      <c r="K16" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>CAQ_D._HORTA</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>D. Horta</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>6</v>
+      </c>
+      <c r="E17" t="n">
+        <v>1</v>
+      </c>
+      <c r="F17" t="n">
+        <v>2</v>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>16.7%</t>
+        </is>
+      </c>
+      <c r="H17" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>28.6%</t>
+        </is>
+      </c>
+      <c r="J17" t="n">
+        <v>2</v>
+      </c>
+      <c r="K17" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>CAQ_I._PAVICEVIC</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>I. Pavicevic</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
         <v>5</v>
       </c>
-      <c r="E13" t="n">
+      <c r="E18" t="n">
+        <v>3</v>
+      </c>
+      <c r="F18" t="n">
+        <v>6</v>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>60.0%</t>
+        </is>
+      </c>
+      <c r="H18" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>35.7%</t>
+        </is>
+      </c>
+      <c r="J18" t="n">
         <v>2</v>
       </c>
-      <c r="F13" t="n">
+      <c r="K18" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>CAQ_A._THIAM</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>A. Thiam</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>5</v>
+      </c>
+      <c r="E19" t="n">
+        <v>2</v>
+      </c>
+      <c r="F19" t="n">
         <v>4</v>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="G19" t="inlineStr">
         <is>
           <t>40.0%</t>
         </is>
       </c>
-      <c r="H13" t="n">
+      <c r="H19" t="n">
         <v>0.8</v>
       </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>22.7%</t>
-        </is>
-      </c>
-      <c r="J13" t="n">
-        <v>3</v>
-      </c>
-      <c r="K13" t="n">
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>13.5%</t>
+        </is>
+      </c>
+      <c r="J19" t="n">
+        <v>4</v>
+      </c>
+      <c r="K19" t="n">
         <v>2</v>
       </c>
     </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>CAQ_J._SHOATS</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>J. Shoats</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>5</v>
+      </c>
+      <c r="E20" t="n">
+        <v>2</v>
+      </c>
+      <c r="F20" t="n">
+        <v>6</v>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>40.0%</t>
+        </is>
+      </c>
+      <c r="H20" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>14.3%</t>
+        </is>
+      </c>
+      <c r="J20" t="n">
+        <v>4</v>
+      </c>
+      <c r="K20" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>CAQ_A._HALLMAN</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>A. Hallman</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>5</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="H21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>29.4%</t>
+        </is>
+      </c>
+      <c r="J21" t="n">
+        <v>2</v>
+      </c>
+      <c r="K21" t="n">
+        <v>2</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:K13"/>
+  <autoFilter ref="A1:K21"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>